--- a/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
@@ -523,6 +523,9 @@
       <c r="A11" t="str">
         <v>3</v>
       </c>
+      <c r="C11" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
@@ -526,6 +526,9 @@
       <c r="C11" t="str">
         <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -584,7 +587,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02010101555510100</v>
+        <v>020101015555101020</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -508,7 +508,7 @@
         <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
       </c>
       <c r="F9" t="str">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -516,7 +516,7 @@
         <v>884_松虫草新品_undefined_undefined_1bunch</v>
       </c>
       <c r="F10" t="str">
-        <v>10</v>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -527,12 +527,96 @@
         <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
       </c>
       <c r="F11" t="str">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>458_蓝盆花白色_Scabiosa caucasica white_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
         <v>20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>754_豌豆花浅粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>502_姜荷花 粉_Curcuma pink_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>4</v>
+      </c>
+      <c r="C15" t="str">
+        <v>388_大丽花_dahlia_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>452_粉吊鸟_pink hanging heliconia_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>5</v>
+      </c>
+      <c r="C17" t="str">
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="C21" t="str" xml:space="preserve">
+        <v xml:space="preserve">509_翠珠粉_Didiscus caeruleus
+pink_Trachymene Coerulea_1bunch</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -587,7 +671,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020101015555101020</v>
+        <v>02010101555520452055101013121450</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
@@ -613,6 +613,9 @@
         <v xml:space="preserve">509_翠珠粉_Didiscus caeruleus
 pink_Trachymene Coerulea_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -671,7 +674,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02010101555520452055101013121450</v>
+        <v>020101015555204520551010131214520</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -566,6 +566,9 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="str">
+        <v>5</v>
+      </c>
       <c r="C16" t="str">
         <v>452_粉吊鸟_pink hanging heliconia_undefined_1bunch</v>
       </c>
@@ -575,7 +578,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" t="str">
         <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
@@ -617,9 +620,95 @@
         <v>20</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>7</v>
+      </c>
+      <c r="C22" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>317_尤加利叶细叶_Eucalyptus Parvifolia_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>8</v>
+      </c>
+      <c r="C25" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>160_卡布奇诺_Cappuccino_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>439_九星叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>9</v>
+      </c>
+      <c r="C30" t="str">
+        <v>522_山归来绿_Smilax china_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>522_山归来绿_Smilax china_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -674,7 +763,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020101015555204520551010131214520</v>
+        <v>02010101555520452055101013121452019101013592020100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
@@ -703,7 +703,7 @@
     </row>
     <row r="31">
       <c r="C31" t="str">
-        <v>522_山归来绿_Smilax china_undefined_1bunch</v>
+        <v>688_山归来橙_undefined_undefined_1bunch</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
@@ -705,6 +705,9 @@
       <c r="C31" t="str">
         <v>688_山归来橙_undefined_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -763,7 +766,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02010101555520452055101013121452019101013592020100</v>
+        <v>02010101555520452055101013121452019101013592020101</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -706,12 +706,92 @@
         <v>688_山归来橙_undefined_undefined_1bunch</v>
       </c>
       <c r="F31" t="str">
-        <v>1</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>877_黄洋金边原色_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>341_南天竹绿_undefined_Nandina domestica Thunb._1bunch</v>
+      </c>
+      <c r="F33" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>422_粉黛_pink muhly grass_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>484_天鹅绒_Star of Bethlehem_undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>328_卢荀草_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F36" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>716_山葡萄_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F37" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>10</v>
+      </c>
+      <c r="C38" t="str">
+        <v>595_玉兰叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F38" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>326_红继木_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F39" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>348_万年青_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F40" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>382_绿朱蕉_Cordyline Snow White Green_undefined_1bunch</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -766,7 +846,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02010101555520452055101013121452019101013592020101</v>
+        <v>0201010155552045205510101312145201910101359202010155510101051015150</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
@@ -788,6 +788,9 @@
       <c r="C41" t="str">
         <v>382_绿朱蕉_Cordyline Snow White Green_undefined_1bunch</v>
       </c>
+      <c r="F41" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -846,7 +849,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0201010155552045205510101312145201910101359202010155510101051015150</v>
+        <v>0201010155552045205510101312145201910101359202010155510101051015155</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L48"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -792,9 +792,67 @@
         <v>5</v>
       </c>
     </row>
+    <row r="42" xml:space="preserve">
+      <c r="C42" t="str" xml:space="preserve">
+        <v xml:space="preserve">404_小飞燕白色_ delphinium ballkleid
+white_undefined_1bunch</v>
+      </c>
+      <c r="F42" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="C43" t="str" xml:space="preserve">
+        <v xml:space="preserve">508_风铃花白色_Canterbury Bells 
+white_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>585_洋牡丹红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>360_夕雾草_undefined_Trachelium caeruleum L._1bunch</v>
+      </c>
+      <c r="F45" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F47" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F48" t="str">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L48"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -849,7 +907,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0201010155552045205510101312145201910101359202010155510101051015155</v>
+        <v>0201010155552045205510101312145201910101359202010155510101051015155201051021520</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-26.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -440,56 +440,53 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" t="str">
-        <v>636_干花大叶白_undefined_undefined_1stem</v>
+        <v>522_山归来绿_Smilax china_undefined_1bunch</v>
       </c>
       <c r="F2" t="str">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="C3" t="str">
-        <v>636_干花大叶白_undefined_undefined_1stem</v>
+        <v>569_灯笼果_undefined_undefined_1bunch</v>
       </c>
       <c r="F3" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="str">
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+      </c>
+      <c r="F4" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>11</v>
+      </c>
+      <c r="C5" t="str">
+        <v>521_商陆_phytolacca acinosa _undefined_1bunch</v>
+      </c>
+      <c r="F5" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="str">
+        <v>403_大飞燕浅蓝色_delphinium light blue_undefined_1bunch</v>
+      </c>
+      <c r="F6" t="str">
         <v>10</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v>636_干花大叶白_undefined_undefined_1stem</v>
-      </c>
-      <c r="F4" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="C5" t="str">
-        <v>636_干花大叶白_undefined_undefined_1stem</v>
-      </c>
-      <c r="F5" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>2</v>
-      </c>
-      <c r="C6" t="str">
-        <v>573_乒乓菊粉_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F6" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="C7" t="str">
-        <v>882_乒乓菊黄_undefined_undefined_1bunch</v>
+        <v>644_唐松草_undefined_undefined_1bunch</v>
       </c>
       <c r="F7" t="str">
         <v>5</v>
@@ -497,362 +494,32 @@
     </row>
     <row r="8">
       <c r="C8" t="str">
-        <v>802_烟花菊粉_undefined_undefined_1bunch</v>
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
       <c r="F8" t="str">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="C9" t="str">
-        <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
       <c r="F9" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="C10" t="str">
-        <v>884_松虫草新品_undefined_undefined_1bunch</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="C10" t="str" xml:space="preserve">
+        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
+white_Trachymene Coerulea_1bunch</v>
       </c>
       <c r="F10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>3</v>
-      </c>
-      <c r="C11" t="str">
-        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
-      </c>
-      <c r="F11" t="str">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="C12" t="str">
-        <v>458_蓝盆花白色_Scabiosa caucasica white_undefined_1bunch</v>
-      </c>
-      <c r="F12" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="C13" t="str">
-        <v>754_豌豆花浅粉_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F13" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="C14" t="str">
-        <v>502_姜荷花 粉_Curcuma pink_undefined_1bunch</v>
-      </c>
-      <c r="F14" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>4</v>
-      </c>
-      <c r="C15" t="str">
-        <v>388_大丽花_dahlia_undefined_1bunch</v>
-      </c>
-      <c r="F15" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>5</v>
-      </c>
-      <c r="C16" t="str">
-        <v>452_粉吊鸟_pink hanging heliconia_undefined_1bunch</v>
-      </c>
-      <c r="F16" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>6</v>
-      </c>
-      <c r="C17" t="str">
-        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F17" t="str">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" t="str">
-        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F18" t="str">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" t="str">
-        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F19" t="str">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" t="str">
-        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F20" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" xml:space="preserve">
-      <c r="C21" t="str" xml:space="preserve">
-        <v xml:space="preserve">509_翠珠粉_Didiscus caeruleus
-pink_Trachymene Coerulea_1bunch</v>
-      </c>
-      <c r="F21" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>7</v>
-      </c>
-      <c r="C22" t="str">
-        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F22" t="str">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" t="str">
-        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F23" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" t="str">
-        <v>317_尤加利叶细叶_Eucalyptus Parvifolia_undefined_1bunch</v>
-      </c>
-      <c r="F24" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>8</v>
-      </c>
-      <c r="C25" t="str">
-        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F25" t="str">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" t="str">
-        <v>160_卡布奇诺_Cappuccino_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F26" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" t="str">
-        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F27" t="str">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" t="str">
-        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F28" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" t="str">
-        <v>439_九星叶_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F29" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>9</v>
-      </c>
-      <c r="C30" t="str">
-        <v>522_山归来绿_Smilax china_undefined_1bunch</v>
-      </c>
-      <c r="F30" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="str">
-        <v>688_山归来橙_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F31" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="str">
-        <v>877_黄洋金边原色_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F32" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="str">
-        <v>341_南天竹绿_undefined_Nandina domestica Thunb._1bunch</v>
-      </c>
-      <c r="F33" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" t="str">
-        <v>422_粉黛_pink muhly grass_undefined_1bunch</v>
-      </c>
-      <c r="F34" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="str">
-        <v>484_天鹅绒_Star of Bethlehem_undefined_1bunch</v>
-      </c>
-      <c r="F35" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="str">
-        <v>328_卢荀草_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F36" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="str">
-        <v>716_山葡萄_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F37" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>10</v>
-      </c>
-      <c r="C38" t="str">
-        <v>595_玉兰叶_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F38" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" t="str">
-        <v>326_红继木_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F39" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="str">
-        <v>348_万年青_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F40" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="str">
-        <v>382_绿朱蕉_Cordyline Snow White Green_undefined_1bunch</v>
-      </c>
-      <c r="F41" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" xml:space="preserve">
-      <c r="C42" t="str" xml:space="preserve">
-        <v xml:space="preserve">404_小飞燕白色_ delphinium ballkleid
-white_undefined_1bunch</v>
-      </c>
-      <c r="F42" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" xml:space="preserve">
-      <c r="C43" t="str" xml:space="preserve">
-        <v xml:space="preserve">508_风铃花白色_Canterbury Bells 
-white_undefined_1bunch</v>
-      </c>
-      <c r="F43" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="str">
-        <v>585_洋牡丹红_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F44" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="str">
-        <v>360_夕雾草_undefined_Trachelium caeruleum L._1bunch</v>
-      </c>
-      <c r="F45" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="str">
-        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F46" t="str">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="str">
-        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F47" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" t="str">
-        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
-      </c>
-      <c r="F48" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -907,7 +574,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0201010155552045205510101312145201910101359202010155510101051015155201051021520</v>
+        <v>0681520105151230</v>
       </c>
     </row>
   </sheetData>
